--- a/03_Outputs/Turistica_Agroecologica/01_Generalidades/distribucion_territorial.xlsx
+++ b/03_Outputs/Turistica_Agroecologica/01_Generalidades/distribucion_territorial.xlsx
@@ -22,7 +22,7 @@
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -32,23 +32,56 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4458A6"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -68,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
     <xf applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0"/>
@@ -77,6 +110,12 @@
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="166" xfId="0"/>
     <xf applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="167" xfId="0"/>
     <xf applyFont="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="2" numFmtId="168" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="4" fontId="4" numFmtId="0" xfId="0"/>
+    <xf applyFont="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0"/>
+    <xf applyFill="1" applyFont="1" borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,15 +441,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="41.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
-    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="42.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,11 +486,11 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>5113</v>
+        <v>5042</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -465,19 +504,19 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>355.210256</v>
+        <v>525.601375</v>
       </c>
       <c r="F2" s="6">
-        <v>0.270050149753842</v>
+        <v>0.285505419940917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>5628</v>
+        <v>5113</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -491,19 +530,19 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>265.764415</v>
+        <v>355.210256</v>
       </c>
       <c r="F3" s="6">
-        <v>0.202048558164357</v>
+        <v>0.192949368343263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>5240</v>
+        <v>5628</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,19 +556,19 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>237.779377</v>
+        <v>265.764415</v>
       </c>
       <c r="F4" s="6">
-        <v>0.180772810701798</v>
+        <v>0.144362599717185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>5656</v>
+        <v>5240</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,19 +582,19 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>161.265719</v>
+        <v>237.779377</v>
       </c>
       <c r="F5" s="6">
-        <v>0.122602967764847</v>
+        <v>0.129161193468481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5347</v>
+        <v>5656</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -569,19 +608,19 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>114.848828</v>
+        <v>161.265719</v>
       </c>
       <c r="F6" s="6">
-        <v>0.0873143234931066</v>
+        <v>0.0875991559671414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5306</v>
+        <v>5347</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -595,64 +634,62 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>93.494441</v>
+        <v>114.848828</v>
       </c>
       <c r="F7" s="6">
-        <v>0.0710795574359815</v>
+        <v>0.0623856108973501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>5306</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E8" s="4">
+        <v>93.494441</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.0507859585410071</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
         <v>5501</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Olaya</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OCCIDENTE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
-        </is>
-      </c>
-      <c r="E8" s="4">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+      <c r="E9" s="4">
         <v>86.986192</v>
       </c>
-      <c r="F8" s="6">
-        <v>0.0661316326860687</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="E9" s="5">
-        <v>1315.349228</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1</v>
+      <c r="F9" s="6">
+        <v>0.0472506931246541</v>
       </c>
     </row>
     <row r="10">
@@ -663,7 +700,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>TOTAL SUBREGIÓN OCCIDENTE</t>
+          <t>TOTAL PROVINCIA TURÍSTICA Y AGROECOLÓGICA</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -677,12 +714,10 @@
         </is>
       </c>
       <c r="E10" s="5">
-        <v>7546.107827</v>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+        <v>1840.950603</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -693,23 +728,53 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>TOTAL SUBREGIÓN OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E11" s="5">
+        <v>7546.107827</v>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>TOTAL DEPARTAMENTO (ANTIOQUIA)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="5">
         <v>62804.710218</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t/>
         </is>
@@ -724,26 +789,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="27.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="28.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>area_km2</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>participacion_area_prov_pct</t>
         </is>
@@ -752,92 +817,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="B2">
-        <v>355.210256</v>
+        <v>525.601375</v>
       </c>
       <c r="C2">
-        <v>0.270050149753842</v>
+        <v>0.285505419940917</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="B3">
-        <v>265.764415</v>
+        <v>355.210256</v>
       </c>
       <c r="C3">
-        <v>0.202048558164357</v>
+        <v>0.192949368343263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="B4">
-        <v>237.779377</v>
+        <v>265.764415</v>
       </c>
       <c r="C4">
-        <v>0.180772810701798</v>
+        <v>0.144362599717185</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="B5">
-        <v>161.265719</v>
+        <v>237.779377</v>
       </c>
       <c r="C5">
-        <v>0.122602967764847</v>
+        <v>0.129161193468481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="B6">
-        <v>114.848828</v>
+        <v>161.265719</v>
       </c>
       <c r="C6">
-        <v>0.0873143234931066</v>
+        <v>0.0875991559671414</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="B7">
-        <v>93.494441</v>
+        <v>114.848828</v>
       </c>
       <c r="C7">
-        <v>0.0710795574359815</v>
+        <v>0.0623856108973501</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>93.494441</v>
+      </c>
+      <c r="C8">
+        <v>0.0507859585410071</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Olaya</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>86.986192</v>
       </c>
-      <c r="C8">
-        <v>0.0661316326860687</v>
+      <c r="C9">
+        <v>0.0472506931246541</v>
       </c>
     </row>
   </sheetData>
@@ -849,32 +927,32 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="35.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="9.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="36.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>ind_mpio</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>subregion</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
@@ -1015,6 +1093,26 @@
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>5042</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Santa Fe de Antioquia</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>PROVINCIA TURISTICA Y AGROECOLOGICA</t>
         </is>
@@ -1029,26 +1127,26 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="11.711"/>
-    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="20.711"/>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="12.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="21.711"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Código DANE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>Área municipal (km²)</t>
         </is>
@@ -1056,92 +1154,105 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>5113</v>
+        <v>5042</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Buriticá</t>
+          <t>Santa Fe de Antioquia</t>
         </is>
       </c>
       <c r="C2">
-        <v>355.210256</v>
+        <v>525.601375</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
-        <v>5628</v>
+        <v>5113</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sabanalarga</t>
+          <t>Buriticá</t>
         </is>
       </c>
       <c r="C3">
-        <v>265.764415</v>
+        <v>355.210256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>5240</v>
+        <v>5628</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ebéjico</t>
+          <t>Sabanalarga</t>
         </is>
       </c>
       <c r="C4">
-        <v>237.779377</v>
+        <v>265.764415</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>5656</v>
+        <v>5240</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>San Jerónimo</t>
+          <t>Ebéjico</t>
         </is>
       </c>
       <c r="C5">
-        <v>161.265719</v>
+        <v>237.779377</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5347</v>
+        <v>5656</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Heliconia</t>
+          <t>San Jerónimo</t>
         </is>
       </c>
       <c r="C6">
-        <v>114.848828</v>
+        <v>161.265719</v>
       </c>
     </row>
     <row r="7">
       <c r="A7">
-        <v>5306</v>
+        <v>5347</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Giraldo</t>
+          <t>Heliconia</t>
         </is>
       </c>
       <c r="C7">
-        <v>93.494441</v>
+        <v>114.848828</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
+        <v>5306</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Giraldo</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>93.494441</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
         <v>5501</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Olaya</t>
         </is>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>86.986192</v>
       </c>
     </row>
